--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/03_Politika, Hedefler ve Yönetim/EKG-YNT-PLN-04_kalite_ve_lojistik_hedefleri_ve_gidisat_plani.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/03_Politika, Hedefler ve Yönetim/EKG-YNT-PLN-04_kalite_ve_lojistik_hedefleri_ve_gidisat_plani.xlsx
@@ -1020,7 +1020,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-PLN-04&amp;C&amp;"Arial,Regular"&amp;11Kalite ve Lojistik Hedefleri ve Gidişat Planı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb81746710bdb410b"/>
   <x:tableParts count="1">
@@ -1425,7 +1426,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-PLN-04&amp;C&amp;"Arial,Regular"&amp;11Kalite ve Lojistik Hedefleri ve Gidişat Planı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a81e8bd7bd9405b"/>
   <x:tableParts count="1">
@@ -1769,7 +1771,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-PLN-04&amp;C&amp;"Arial,Regular"&amp;11Kalite ve Lojistik Hedefleri ve Gidişat Planı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89738abe984a461e"/>
   <x:tableParts count="1">
